--- a/diseases/d023/2026-2029.xlsx
+++ b/diseases/d023/2026-2029.xlsx
@@ -13717,6 +13717,154 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
+      <c r="AT90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13750,7 +13898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -13833,7 +13981,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -13843,7 +13991,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d023/2026-2029.xlsx
+++ b/diseases/d023/2026-2029.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1209,9 +1206,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -2985,9 +2979,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3133,9 +3124,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4761,9 +4749,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -4909,9 +4894,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6241,9 +6223,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6537,9 +6516,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -6685,9 +6661,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8017,9 +7990,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8313,9 +8283,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8461,9 +8428,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -10089,9 +10053,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10385,9 +10346,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10533,9 +10491,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -10681,9 +10636,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -10829,9 +10781,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -10977,9 +10926,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11125,9 +11071,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -11273,9 +11216,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -11421,9 +11361,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -11569,9 +11506,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -11717,9 +11651,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -11865,9 +11796,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12013,9 +11941,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -12161,9 +12086,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -12309,9 +12231,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -12457,9 +12376,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -12605,9 +12521,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -12753,9 +12666,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -12901,9 +12811,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -13049,9 +12956,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13197,9 +13101,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -13345,9 +13246,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -13493,9 +13391,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -13641,9 +13536,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -13787,9 +13679,6 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">

--- a/diseases/d023/2026-2029.xlsx
+++ b/diseases/d023/2026-2029.xlsx
@@ -13754,6 +13754,151 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13787,7 +13932,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -13870,7 +14015,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -13880,7 +14025,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d023/2026-2029.xlsx
+++ b/diseases/d023/2026-2029.xlsx
@@ -11897,12 +11897,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11936,13 +11936,16 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>0.00559128121398161</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -11975,42 +11978,42 @@
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -12042,12 +12045,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12072,7 +12075,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -12120,42 +12123,42 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12190,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12265,42 +12268,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12332,12 +12335,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12362,7 +12365,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -12410,42 +12413,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -12477,12 +12480,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12555,42 +12558,42 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12622,12 +12625,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12652,7 +12655,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -12700,42 +12703,42 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -12767,12 +12770,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12845,42 +12848,42 @@
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12912,12 +12915,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -12942,7 +12945,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -12990,42 +12993,42 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13057,12 +13060,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -13135,42 +13138,42 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13202,12 +13205,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -13232,7 +13235,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -13280,42 +13283,42 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13347,12 +13350,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13377,12 +13380,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -13425,42 +13428,42 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13492,12 +13495,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -13570,42 +13573,42 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13637,12 +13640,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -13667,7 +13670,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -13715,42 +13718,42 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -13812,7 +13815,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -13894,6 +13897,151 @@
         </is>
       </c>
       <c r="BC91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -14015,7 +14163,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -14025,7 +14173,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -14077,7 +14225,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>102</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16">
@@ -14087,7 +14235,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d023/2026-2029.xlsx
+++ b/diseases/d023/2026-2029.xlsx
@@ -14047,6 +14047,151 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14080,7 +14225,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14163,7 +14308,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -14173,7 +14318,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d023/2026-2029.xlsx
+++ b/diseases/d023/2026-2029.xlsx
@@ -12045,12 +12045,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12123,42 +12123,42 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12190,12 +12190,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12220,7 +12220,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -12268,42 +12268,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12335,12 +12335,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12413,42 +12413,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12480,12 +12480,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -12558,42 +12558,42 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -12625,12 +12625,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12703,42 +12703,42 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12770,12 +12770,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -12848,42 +12848,42 @@
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -12915,12 +12915,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -12993,42 +12993,42 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -13138,42 +13138,42 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13205,12 +13205,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -13283,42 +13283,42 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13350,12 +13350,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -13428,42 +13428,42 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13495,12 +13495,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -13573,42 +13573,42 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13640,12 +13640,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -13718,42 +13718,42 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13785,12 +13785,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -13863,42 +13863,42 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -14187,6 +14187,151 @@
         </is>
       </c>
       <c r="BC93" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -14308,7 +14453,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -14318,7 +14463,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d023/2026-2029.xlsx
+++ b/diseases/d023/2026-2029.xlsx
@@ -10154,12 +10154,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10193,20 +10193,14 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0.001627841366095912</v>
+        <v>0</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10235,42 +10229,42 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10302,12 +10296,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10346,12 +10340,9 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -10380,42 +10371,42 @@
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10447,12 +10438,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10491,12 +10482,9 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -10525,42 +10513,42 @@
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10592,12 +10580,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10622,7 +10610,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -10636,12 +10624,9 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -10670,42 +10655,42 @@
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10737,12 +10722,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10767,7 +10752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -10781,12 +10766,9 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -10815,42 +10797,42 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10882,12 +10864,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10912,7 +10894,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -10926,12 +10908,9 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -10960,42 +10939,42 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11006,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11057,7 +11036,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -11071,12 +11050,9 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11105,42 +11081,42 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11172,12 +11148,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11202,7 +11178,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -11216,12 +11192,9 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -11250,42 +11223,42 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11317,12 +11290,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11347,7 +11320,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -11356,13 +11329,16 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O74" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>0.001627841366095912</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -11395,42 +11371,42 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11438,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11492,7 +11468,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -11540,42 +11516,42 @@
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11607,12 +11583,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11637,7 +11613,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -11685,42 +11661,42 @@
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -11752,12 +11728,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11782,12 +11758,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -11830,42 +11806,42 @@
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11873,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11927,25 +11903,22 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>79</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0.00559128121398161</v>
+        <v>0</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -11978,42 +11951,42 @@
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -12045,12 +12018,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12075,12 +12048,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -12123,42 +12096,42 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12190,12 +12163,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12220,12 +12193,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -12268,42 +12241,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -12365,12 +12338,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -12510,12 +12483,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -12655,12 +12628,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -12800,12 +12773,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -12915,12 +12888,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -12945,7 +12918,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -12993,42 +12966,42 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13033,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -13090,7 +13063,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -13104,12 +13077,9 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -13138,42 +13108,42 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13205,12 +13175,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -13235,7 +13205,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -13249,12 +13219,9 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -13283,42 +13250,42 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13350,12 +13317,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13380,7 +13347,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -13394,12 +13361,9 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -13428,42 +13392,42 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13495,12 +13459,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -13525,7 +13489,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -13539,12 +13503,9 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -13573,42 +13534,42 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13640,12 +13601,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -13670,12 +13631,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N90" t="n">
@@ -13684,12 +13645,9 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -13723,12 +13681,12 @@
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -13743,12 +13701,12 @@
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
@@ -13785,12 +13743,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13815,12 +13773,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -13829,12 +13787,9 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -13863,42 +13818,42 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13930,12 +13885,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -13960,12 +13915,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -13974,12 +13929,9 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -14008,42 +13960,42 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14075,12 +14027,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -14105,12 +14057,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -14119,12 +14071,9 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -14153,42 +14102,42 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14220,12 +14169,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -14250,22 +14199,25 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>0.00559128121398161</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -14298,42 +14250,3933 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW94" t="inlineStr">
+      <c r="AW97" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
+      <c r="AX97" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY94" t="inlineStr">
+      <c r="AY97" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
+      <c r="AZ97" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA94" t="inlineStr">
+      <c r="BA97" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB94" t="inlineStr">
+      <c r="BB97" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC94" t="inlineStr">
+      <c r="BC97" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
+      <c r="AT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
+      <c r="AT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
+      <c r="AT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
+      <c r="AT111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr"/>
+      <c r="AT113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr"/>
+      <c r="AT114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
+      <c r="AT115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
+      <c r="AT116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
+      <c r="AT117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
+      <c r="AT118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14370,7 +18213,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -14453,7 +18296,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -14463,7 +18306,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
